--- a/12624290 .xlsx
+++ b/12624290 .xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -208,17 +208,20 @@
   <si>
     <t>I slept for 3 hours.</t>
   </si>
+  <si>
+    <t>feeling low</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="32">
     <font>
@@ -309,16 +312,38 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -340,13 +365,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -356,22 +374,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -379,15 +382,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -402,29 +405,21 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -445,8 +440,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -473,7 +476,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -485,37 +548,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -533,19 +566,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -557,13 +584,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -575,25 +632,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -605,43 +644,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -653,7 +656,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -682,6 +685,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -706,15 +718,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -726,17 +729,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -758,9 +750,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -779,148 +773,157 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -936,7 +939,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1856,23 +1859,41 @@
       <c r="C11" s="8">
         <v>30</v>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
+      <c r="D11" s="8">
+        <v>90</v>
+      </c>
+      <c r="E11" s="8">
+        <v>30</v>
+      </c>
+      <c r="F11" s="8">
+        <v>300</v>
+      </c>
+      <c r="G11" s="8">
+        <v>6</v>
+      </c>
+      <c r="H11" s="8">
+        <v>90</v>
+      </c>
       <c r="I11" s="11">
         <f t="shared" si="0"/>
-        <v>390</v>
+        <v>900</v>
       </c>
       <c r="J11" s="11">
         <f t="shared" si="1"/>
-        <v>1050</v>
-      </c>
-      <c r="K11" s="12"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="12"/>
-      <c r="N11" s="14"/>
+        <v>540</v>
+      </c>
+      <c r="K11" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="L11" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="M11" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="N11" s="14" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="6">
@@ -11033,11 +11054,11 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6 L7:L392">
+      <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6 M7:M392">
       <formula1>"High,Medium,Low"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6 L7:L392">
-      <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6 K7:K392">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>

--- a/12624290 .xlsx
+++ b/12624290 .xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -211,6 +211,9 @@
   <si>
     <t>feeling low</t>
   </si>
+  <si>
+    <t>Mising home.</t>
+  </si>
 </sst>
 </file>
 
@@ -218,9 +221,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="32">
@@ -319,36 +322,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -357,79 +330,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -449,9 +353,108 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -476,7 +479,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,73 +605,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -566,97 +659,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -689,7 +692,57 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -712,49 +765,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -773,154 +785,145 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1899,25 +1902,47 @@
       <c r="A12" s="6">
         <v>46260</v>
       </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="11" t="str">
+      <c r="B12" s="8">
+        <v>300</v>
+      </c>
+      <c r="C12" s="8">
+        <v>40</v>
+      </c>
+      <c r="D12" s="8">
+        <v>60</v>
+      </c>
+      <c r="E12" s="8">
+        <v>30</v>
+      </c>
+      <c r="F12" s="8">
+        <v>300</v>
+      </c>
+      <c r="G12" s="8">
+        <v>6</v>
+      </c>
+      <c r="H12" s="8">
+        <v>60</v>
+      </c>
+      <c r="I12" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="11" t="str">
+        <v>790</v>
+      </c>
+      <c r="J12" s="11">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="12"/>
-      <c r="N12" s="14"/>
+        <v>650</v>
+      </c>
+      <c r="K12" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="L12" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="M12" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="N12" s="14" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="6">
@@ -11054,11 +11079,11 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6 M7:M392">
+      <formula1>"High,Medium,Low"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6 L7:L392">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6 M7:M392">
-      <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6 K7:K392">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
